--- a/product_upload/packages/8/file.xlsx
+++ b/product_upload/packages/8/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -842,6 +847,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>TRACLEER 125 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-69EC6F7941B0</t>
         </is>
       </c>
@@ -865,7 +875,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1036,6 +1046,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>TOVAST 40 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-16D9EE04EF4E</t>
         </is>
       </c>
@@ -1059,7 +1074,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1230,6 +1245,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>TOVAST 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-A061F2EB9BDA</t>
         </is>
       </c>
@@ -1253,7 +1273,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1424,6 +1444,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>TOVAST 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-5382B0F5552B</t>
         </is>
       </c>
@@ -1447,7 +1472,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1612,6 +1637,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>TORVACOL 40MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-6E0E38840913</t>
         </is>
       </c>
@@ -1635,7 +1665,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1796,6 +1826,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>TORVACOL 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-1653EB09AD65</t>
         </is>
       </c>
@@ -1819,7 +1854,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1984,6 +2019,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>TORVACOL 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-80A2732F5622</t>
         </is>
       </c>
@@ -2007,7 +2047,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2174,6 +2214,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>TRAJENTA 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-9ACFCF2209C3</t>
         </is>
       </c>
@@ -2197,7 +2242,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2364,6 +2409,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>TRIPACEL VACCINE</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-C33845DAFF80</t>
         </is>
       </c>
@@ -2387,7 +2437,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2546,6 +2596,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>TRIO BE TABLET</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-FFB5AD696ECC</t>
         </is>
       </c>
@@ -2569,7 +2624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2734,6 +2789,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>TOPRAZOLE 40 MG E.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-71B184E5A6F0</t>
         </is>
       </c>
@@ -2757,7 +2817,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2928,6 +2988,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>TRENTAL TAB 400MG</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-4988BEA9DE97</t>
         </is>
       </c>
@@ -2951,7 +3016,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3122,6 +3187,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>TRENTAL TAB 400MG</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-8F882D89B57B</t>
         </is>
       </c>
@@ -3145,7 +3215,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3310,6 +3380,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>TOPRAZOLE 40 MG E.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-94361ACB8CDD</t>
         </is>
       </c>
@@ -3333,7 +3408,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3500,6 +3575,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>TIGER BALSAM</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-0CF8AD92D886</t>
         </is>
       </c>
@@ -3523,7 +3603,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3678,6 +3758,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>TIGER BALSAM</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-722FAFB8407C</t>
         </is>
       </c>
@@ -3701,7 +3786,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3866,6 +3951,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>TIDILOR 5 MG - 5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-B27457DB8C72</t>
         </is>
       </c>
@@ -3889,7 +3979,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4050,6 +4140,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>TIDILOR 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-9BBCB6308B92</t>
         </is>
       </c>
@@ -4073,7 +4168,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4246,6 +4341,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>TICANASE 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-41AC5C809CA5</t>
         </is>
       </c>
@@ -4269,7 +4369,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4426,6 +4526,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>THEO-DUR TAB 300MG</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-BD5E1F08CDDF</t>
         </is>
       </c>
@@ -4449,7 +4554,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4606,6 +4711,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>THEO-DUR TAB 200MG</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-0C2840C4FE3B</t>
         </is>
       </c>
@@ -4629,7 +4739,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>TEVETEN PLUS 600-12.5MG FILM COATED TAB.</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-C9F6028DBCBD</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4986,6 +5101,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>TILAX 2 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-A9E9C85787BD</t>
         </is>
       </c>
@@ -5009,7 +5129,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5174,6 +5294,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>TILAX 4 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-EEC115EF982B</t>
         </is>
       </c>
@@ -5197,7 +5322,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5362,6 +5487,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>TILCOTIL TAB 20MG</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-2FE5556DA2F1</t>
         </is>
       </c>
@@ -5385,7 +5515,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5542,6 +5672,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>TOPAMAX 25MG-TAB. F.C.TAB.</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-821EE810DEC0</t>
         </is>
       </c>
@@ -5565,7 +5700,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5722,6 +5857,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>TOPAMAX 200MG F.C.TAB.</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-A9ECA1E2C610</t>
         </is>
       </c>
@@ -5745,7 +5885,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5908,6 +6048,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>TOPAMAX 15MG SPRINKLE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-C12E6FD8FF6D</t>
         </is>
       </c>
@@ -5931,7 +6076,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6088,6 +6233,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>TOPAMAX 100MG F.C.TAB.</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-4F17D81EA24F</t>
         </is>
       </c>
@@ -6111,7 +6261,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6276,6 +6426,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>TOPRAZOLE 20MG ENTERIC COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-E6DFC76908FA</t>
         </is>
       </c>
@@ -6299,7 +6454,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6464,6 +6619,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>TOFRANIL 25 MG 50 TAB</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-229E4B4E57C7</t>
         </is>
       </c>
@@ -6487,7 +6647,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6652,6 +6812,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>TOBRACIN 0.3% EYE OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-6FF88F9D665B</t>
         </is>
       </c>
@@ -6675,7 +6840,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6844,6 +7009,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>TOBRACIN 0.3% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-38DDF0BA49A3</t>
         </is>
       </c>
@@ -6867,7 +7037,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7028,6 +7198,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>TIVICAY 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-CCCD9A4DDBC5</t>
         </is>
       </c>
@@ -7051,7 +7226,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7224,6 +7399,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>VIDROP ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-DB681D3C2F80</t>
         </is>
       </c>
@@ -7247,7 +7427,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7408,6 +7588,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>VIFOLIN TAB 5 MG</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-D0AA8E31B3B5</t>
         </is>
       </c>
@@ -7431,7 +7616,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7592,6 +7777,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ZINOPRIL 20 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-AA019D8FD173</t>
         </is>
       </c>
@@ -7615,7 +7805,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7780,6 +7970,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ZINOPRIL 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-8D6450B26112</t>
         </is>
       </c>
@@ -7803,7 +7998,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7972,6 +8167,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>ZINNAT</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-205CD56B9857</t>
         </is>
       </c>
@@ -7995,7 +8195,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8164,6 +8364,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ZINNAT</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-0C89BC83E44E</t>
         </is>
       </c>
@@ -8187,7 +8392,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8356,6 +8561,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ZINNAT</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-AADCE9742649</t>
         </is>
       </c>
@@ -8379,7 +8589,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8548,6 +8758,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ZINNAT</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-4946C65F3117</t>
         </is>
       </c>
@@ -8571,7 +8786,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8740,6 +8955,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>AZOLID 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-F1F76C2FFEE2</t>
         </is>
       </c>
@@ -8763,7 +8983,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8924,6 +9144,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>AZOLID 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-A69012A0928B</t>
         </is>
       </c>
@@ -8947,7 +9172,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9116,6 +9341,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ZIMAX 250MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-A3F1AFB2ACDF</t>
         </is>
       </c>
@@ -9139,7 +9369,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9300,6 +9530,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ZIMAX 250MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-9A9F8D1E0AC5</t>
         </is>
       </c>
@@ -9323,7 +9558,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9480,6 +9715,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ZINOPRIL 5 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-AD91E5B23470</t>
         </is>
       </c>
@@ -9503,7 +9743,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9664,6 +9904,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ZINOXIMOR 125MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-7725BA1C3805</t>
         </is>
       </c>
@@ -9687,7 +9932,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9852,6 +10097,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ZOCIN 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-9163C5166677</t>
         </is>
       </c>
@@ -9875,7 +10125,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10032,6 +10282,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>ZOCIN 300 mg/7.5 ml suspension</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-B00255DDDA91</t>
         </is>
       </c>
@@ -10055,7 +10310,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10212,6 +10467,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ZIMAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-1541EF501AD4</t>
         </is>
       </c>
@@ -10235,7 +10495,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10392,6 +10652,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ZOCIN 200MG-5ML POW. FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-6348A4628B57</t>
         </is>
       </c>
@@ -10415,7 +10680,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10586,6 +10851,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ZITHROMAX 250MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-66DD4F773CAC</t>
         </is>
       </c>
@@ -10609,7 +10879,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10784,6 +11054,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ZITHROMAX 250MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-088FD8C7EB55</t>
         </is>
       </c>
@@ -10807,7 +11082,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10978,6 +11253,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ZITHROMAX 200MG-5ML SUSP.AFTER RECONSTIT</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-FBE191B9102D</t>
         </is>
       </c>
@@ -11001,7 +11281,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11172,6 +11452,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>ZITHROMAX 200MG-5ML SUSP.AFTER RECONSTIT</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-0942AF90C97D</t>
         </is>
       </c>
@@ -11195,7 +11480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11366,6 +11651,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>ZITHROMAX 200MG-5ML SUSP.AFTER RECONSTIT</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-0F784BB132BF</t>
         </is>
       </c>
@@ -11389,7 +11679,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11558,6 +11848,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>ZINOXIMOR 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-FAFE78939C75</t>
         </is>
       </c>
@@ -11581,7 +11876,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11746,6 +12041,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>ZINOXIMOR 250 MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-84E259D12249</t>
         </is>
       </c>
@@ -11769,7 +12069,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11934,6 +12234,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>ZIMAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-ED2CC10A9F6D</t>
         </is>
       </c>
@@ -11957,7 +12262,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12114,6 +12419,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>ZEROX 200MG-5ML POWDER FOR ORAL SUSP.</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-9C3A3CF8DC24</t>
         </is>
       </c>
@@ -12137,7 +12447,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12302,6 +12612,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>ZENORIT 8 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-7063CA5248E6</t>
         </is>
       </c>
@@ -12325,7 +12640,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12478,6 +12793,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ZEMITRON 8MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-AEDCBA74B9DC</t>
         </is>
       </c>
@@ -12501,7 +12821,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12662,6 +12982,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ZEMITRON 4MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-6613E8426227</t>
         </is>
       </c>
@@ -12685,7 +13010,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12846,6 +13171,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ZELAX 20MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-173026BEAD61</t>
         </is>
       </c>
@@ -12869,7 +13199,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13034,6 +13364,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ZELAX 10MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-F456B555A0CD</t>
         </is>
       </c>
@@ -13057,7 +13392,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13224,6 +13559,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ZEFFIX</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-140634EEAE33</t>
         </is>
       </c>
@@ -13247,7 +13587,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13404,6 +13744,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>ZEROX 200MG-5ML POWDER FOR ORAL SUSP.</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-3EDAD5BD13C4</t>
         </is>
       </c>
@@ -13427,7 +13772,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13580,6 +13925,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>ZEROX 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-1BE8AD8328E8</t>
         </is>
       </c>
@@ -13603,7 +13953,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13756,6 +14106,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>ZEROX 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-3BC44D3CC969</t>
         </is>
       </c>
@@ -13779,7 +14134,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13944,6 +14299,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>ZERTAZINE 5MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-0BE45D13FD9C</t>
         </is>
       </c>
@@ -13967,7 +14327,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14128,6 +14488,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ZIAGEN 300MG TAB</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-C3D60E7EEE14</t>
         </is>
       </c>
@@ -14151,7 +14516,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14312,6 +14677,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ZETRON 250 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-DECD2923C658</t>
         </is>
       </c>
@@ -14335,7 +14705,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14492,6 +14862,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t xml:space="preserve"> ZETRON 300 per 7.5 ml</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-1039F9EADB81</t>
         </is>
       </c>
@@ -14515,7 +14890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14680,6 +15055,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>ZETRON 200 mg per 5 ml</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-7EDB78C3AB77</t>
         </is>
       </c>
@@ -14703,7 +15083,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14864,6 +15244,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>ZETEX 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-F439DF7A7791</t>
         </is>
       </c>
@@ -14887,7 +15272,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15048,6 +15433,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>ZIMAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-45207816749E</t>
         </is>
       </c>
@@ -15071,7 +15461,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15234,6 +15624,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>ZETACORT CREAM</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-7468C4A3DC1C</t>
         </is>
       </c>
@@ -15257,7 +15652,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15414,6 +15809,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>ZETA 20MG OINTMENT TUBE</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-F50ACDEA2150</t>
         </is>
       </c>
@@ -15437,7 +15837,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15602,6 +16002,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>ZESTRIL 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-A4F258AA8980</t>
         </is>
       </c>
@@ -15625,7 +16030,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15794,6 +16199,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ZESTRIL 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-4CD9D7B393D5</t>
         </is>
       </c>
@@ -15817,7 +16227,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15982,6 +16392,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ZESTRIL 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-A40116081861</t>
         </is>
       </c>
@@ -16005,7 +16420,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16170,6 +16585,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ZERTAZINE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-6D1DD9112A28</t>
         </is>
       </c>
@@ -16193,7 +16613,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16350,6 +16770,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ZERTAZINE</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-63F1A1903BB5</t>
         </is>
       </c>
@@ -16373,7 +16798,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16530,6 +16955,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>ZETA 20MG-GM CREAM</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-4236064807C6</t>
         </is>
       </c>
@@ -16553,7 +16983,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16718,6 +17148,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>ZOLPIGEN</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-682F410FE004</t>
         </is>
       </c>
@@ -16741,7 +17176,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16902,6 +17337,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>ZOMIDOR 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-E655D3B08083</t>
         </is>
       </c>
@@ -16925,7 +17365,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17086,6 +17526,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-9D27C92EC207</t>
         </is>
       </c>
@@ -17109,7 +17554,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17262,6 +17707,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-52A3BBDA42A8</t>
         </is>
       </c>
@@ -17285,7 +17735,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17446,6 +17896,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>HYDROLYTE ORAL REHYDRATION SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-DF6E0C1DCF81</t>
         </is>
       </c>
@@ -17469,7 +17924,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17638,6 +18093,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>LIPICURE 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-52A52FFFCD00</t>
         </is>
       </c>
@@ -17661,7 +18121,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17830,6 +18290,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>LIPICURE 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-D78DF5A9389D</t>
         </is>
       </c>
@@ -17853,7 +18318,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18022,6 +18487,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>LIPICURE 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-E59D94AC549F</t>
         </is>
       </c>
@@ -18045,7 +18515,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18216,6 +18686,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>RENNIE TAB</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-D23F91AB30EE</t>
         </is>
       </c>
@@ -18239,7 +18714,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18400,6 +18875,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-8F4F10BB7846</t>
         </is>
       </c>
@@ -18423,7 +18903,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18576,6 +19056,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-E13BA1DCBBC4</t>
         </is>
       </c>
@@ -18599,7 +19084,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18752,6 +19237,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>IRBETEL 150 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-9B2E0812271E</t>
         </is>
       </c>
@@ -18775,7 +19265,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18930,6 +19420,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>CO-IRBETEL 162.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-A3EC3E613122</t>
         </is>
       </c>
@@ -18953,7 +19448,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19112,6 +19607,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-F26CD4751D92</t>
         </is>
       </c>
@@ -19135,7 +19635,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19293,6 +19793,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-39C137E4D93D</t>
         </is>
@@ -19309,7 +19814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19355,100 +19860,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19480,7 +19990,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19495,92 +20005,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-28105</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>313.53</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>708</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19612,7 +20127,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19627,92 +20142,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-20570</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>121.87</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>709</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19744,7 +20264,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19759,92 +20279,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-86074</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>121.42</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Medical Bed / Mattress</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>710</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19876,7 +20401,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19891,92 +20416,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-80844</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>257.48</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>711</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20008,7 +20538,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20023,92 +20553,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-62772</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>321.62</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Medical Bed / Mattress</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>712</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20140,7 +20675,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20155,92 +20690,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-73520</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>251.11</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Medical Bed / Mattress</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>713</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20272,7 +20812,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20287,92 +20827,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-54194</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>307.12</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>714</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20404,7 +20949,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20419,92 +20964,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-57317</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>299.15</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>715</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20536,7 +21086,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20551,92 +21101,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-10976</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>228.27</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>716</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20668,7 +21223,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20683,92 +21238,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-93131</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>30.8</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>717</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20800,7 +21360,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20815,92 +21375,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-36585</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>380.14</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>718</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20932,7 +21497,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20947,92 +21512,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-18387</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>435.17</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>719</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21049,7 +21619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21155,6 +21725,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21190,7 +21770,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21255,6 +21835,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-8DC8760F6151</t>
         </is>
@@ -21291,7 +21881,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21356,6 +21946,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-8C9A80E68335</t>
         </is>
@@ -21392,7 +21992,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21457,6 +22057,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-7E94D772BE12</t>
         </is>
@@ -21493,7 +22103,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21558,6 +22168,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-4ADC06F92A1A</t>
         </is>
@@ -21594,7 +22214,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21659,6 +22279,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-22DCE494CFA9</t>
         </is>
@@ -21695,7 +22325,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21760,6 +22390,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-D40794207D2E</t>
         </is>
@@ -21796,7 +22436,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21861,6 +22501,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-C3C2F83B205E</t>
         </is>
@@ -21897,7 +22547,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21962,6 +22612,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-DC2F2ECAE7DC</t>
         </is>
@@ -21998,7 +22658,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22063,6 +22723,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-22D0A7C5D6C9</t>
         </is>
@@ -22099,7 +22769,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22164,6 +22834,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-40B00481C159</t>
         </is>
@@ -22200,7 +22880,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22265,6 +22945,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-DBEE440179B9</t>
         </is>
@@ -22301,7 +22991,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22366,6 +23056,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-A863B7509137</t>
         </is>
@@ -22402,7 +23102,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22467,6 +23167,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-6BEB076C7702</t>
         </is>
@@ -22503,7 +23213,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22568,6 +23278,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-0B0EAD078430</t>
         </is>
@@ -22604,7 +23324,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22669,6 +23389,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-CB9C595DFD13</t>
         </is>
@@ -22705,7 +23435,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22770,6 +23500,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-EA40AF6E46CB</t>
         </is>
@@ -22806,7 +23546,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22871,6 +23611,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-4365AD6D77D6</t>
         </is>
@@ -22907,7 +23657,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22972,6 +23722,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-0CBCC0572731</t>
         </is>
@@ -23008,7 +23768,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23073,6 +23833,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-2B03B82A2CA3</t>
         </is>
@@ -23109,7 +23879,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23174,6 +23944,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-3206188A6EAC</t>
         </is>

--- a/product_upload/packages/8/file.xlsx
+++ b/product_upload/packages/8/file.xlsx
@@ -1673,8 +1673,16 @@
           <t>7402103626-289-268641165894</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TORVACOL 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TORVACOL 20MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2445,8 +2453,16 @@
           <t>2676580471-970-178982543995</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIO BE TABLET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TRIO BE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -3611,8 +3627,16 @@
           <t>5736284842-111-628385595696</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIGER BALSAM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TIGER BALSAM detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3794,8 +3818,16 @@
           <t>1924862758-101-603218870781</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIDILOR 5 MG - 5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TIDILOR 5 MG - 5 ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3987,8 +4019,16 @@
           <t>0636513899-694-053617323329</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIDILOR 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TIDILOR 10MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4377,8 +4417,16 @@
           <t>3528910301-857-511235779456</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ THEO-DUR TAB 300MG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>THEO-DUR TAB 300MG detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4562,8 +4610,16 @@
           <t>9007861480-667-481702233874</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ THEO-DUR TAB 200MG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>THEO-DUR TAB 200MG detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -5330,8 +5386,16 @@
           <t>2322465839-560-215301729368</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TILCOTIL TAB 20MG</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TILCOTIL TAB 20MG detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5523,8 +5587,16 @@
           <t>6595198810-527-795311343863</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOPAMAX 25MG-TAB. F.C.TAB.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TOPAMAX 25MG-TAB. F.C.TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5708,8 +5780,16 @@
           <t>5095130637-599-588682120479</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOPAMAX 200MG F.C.TAB.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TOPAMAX 200MG F.C.TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5893,8 +5973,16 @@
           <t>4125308664-121-868079167949</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOPAMAX 15MG SPRINKLE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TOPAMAX 15MG SPRINKLE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>RIYADH PHARMA</t>
@@ -6084,8 +6172,16 @@
           <t>4967985873-477-949058204372</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOPAMAX 100MG F.C.TAB.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TOPAMAX 100MG F.C.TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -7045,8 +7141,16 @@
           <t>7350816557-451-604488428516</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIVICAY 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TIVICAY 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7435,8 +7539,16 @@
           <t>9252978639-989-631804501615</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIFOLIN TAB 5 MG</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VIFOLIN TAB 5 MG detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -8991,8 +9103,16 @@
           <t>0784339137-250-654784776326</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZOLID 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AZOLID 250MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9377,8 +9497,16 @@
           <t>3483698659-713-705311786064</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZIMAX 250MG CAP.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ZIMAX 250MG CAP. detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9566,8 +9694,16 @@
           <t>3065609434-957-403714939132</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOPRIL 5 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ZINOPRIL 5 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9751,8 +9887,16 @@
           <t>3623370853-758-942799938951</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOXIMOR 125MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ZINOXIMOR 125MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10133,8 +10277,16 @@
           <t>8587392508-840-888241202744</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOCIN 300 mg/7.5 ml suspension</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ZOCIN 300 mg/7.5 ml suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10318,8 +10470,16 @@
           <t>3951615670-462-180521567062</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZIMAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ZIMAX 200MG\5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10503,8 +10663,16 @@
           <t>6477962595-890-985984437548</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOCIN 200MG-5ML POW. FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ZOCIN 200MG-5ML POW. FOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -12270,8 +12438,16 @@
           <t>8420796879-691-256200640393</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEROX 200MG-5ML POWDER FOR ORAL SUSP.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ZEROX 200MG-5ML POWDER FOR ORAL SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12648,8 +12824,16 @@
           <t>0419894377-998-844111691747</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEMITRON 8MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ZEMITRON 8MG F-C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12829,8 +13013,16 @@
           <t>1495186233-803-916969461307</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEMITRON 4MG F-C TABLET</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ZEMITRON 4MG F-C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13018,8 +13210,16 @@
           <t>0896880653-102-314048186159</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZELAX 20MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ZELAX 20MG FILM COATED CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13207,8 +13407,16 @@
           <t>9409382167-910-398132878653</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZELAX 10MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ZELAX 10MG FILM COATED CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13595,8 +13803,16 @@
           <t>4146386873-804-720029193760</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEROX 200MG-5ML POWDER FOR ORAL SUSP.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ZEROX 200MG-5ML POWDER FOR ORAL SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13780,8 +13996,16 @@
           <t>2527822244-291-233663868764</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEROX 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ZEROX 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13961,8 +14185,16 @@
           <t>9636582082-618-148125521573</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEROX 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ZEROX 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14335,8 +14567,16 @@
           <t>2421436313-147-446037517707</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZIAGEN 300MG TAB</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ZIAGEN 300MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14713,8 +14953,16 @@
           <t>4576196783-157-606664424003</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZETRON 300 per 7.5 ml</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ZETRON 300 per 7.5 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15469,8 +15717,16 @@
           <t>9488860569-213-514869836147</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZETACORT CREAM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ZETACORT CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15660,8 +15916,16 @@
           <t>4322198493-885-652427360715</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZETA 20MG OINTMENT TUBE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ZETA 20MG OINTMENT TUBE detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16621,8 +16885,16 @@
           <t>7500746193-005-095443190819</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZERTAZINE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ZERTAZINE detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16806,8 +17078,16 @@
           <t>3707974341-293-078864335424</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZETA 20MG-GM CREAM</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ZETA 20MG-GM CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17184,8 +17464,16 @@
           <t>0788862670-063-024576306197</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOMIDOR 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ZOMIDOR 2% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17373,8 +17661,16 @@
           <t>5016805626-797-705253468003</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>LOCASONE 0.1% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17562,8 +17858,16 @@
           <t>3578808656-514-168021394924</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>LOCASONE 0.1% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17743,8 +18047,16 @@
           <t>7269500079-754-446077835857</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYDROLYTE ORAL REHYDRATION SOLUTION</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>HYDROLYTE ORAL REHYDRATION SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18722,8 +19034,16 @@
           <t>9494949901-883-175488388546</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>LOCASONE 0.1% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18911,8 +19231,16 @@
           <t>3287733312-714-901605473071</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE 0.1% cream</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>LOCASONE 0.1% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19092,8 +19420,16 @@
           <t>2017667716-765-656374937241</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBETEL 150 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>IRBETEL 150 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19273,8 +19609,16 @@
           <t>8759022179-930-263327976691</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-IRBETEL 162.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CO-IRBETEL 162.5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19456,8 +19800,16 @@
           <t>8848947099-710-818857090153</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CO-VALISTA detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19643,8 +19995,16 @@
           <t>5033849878-877-649161657398</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CO-VALISTA detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/8/file.xlsx
+++ b/product_upload/packages/8/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21979,7 +21979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22060,40 +22060,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22173,38 +22178,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>318.59</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-8DC8760F6151</t>
         </is>
@@ -22284,38 +22294,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>367.36</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-8C9A80E68335</t>
         </is>
@@ -22395,38 +22410,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>134.92</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-7E94D772BE12</t>
         </is>
@@ -22506,38 +22526,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>367.79</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-4ADC06F92A1A</t>
         </is>
@@ -22617,38 +22642,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>460.87</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-22DCE494CFA9</t>
         </is>
@@ -22728,38 +22758,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>285.13</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-D40794207D2E</t>
         </is>
@@ -22839,38 +22874,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>87.09</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-C3C2F83B205E</t>
         </is>
@@ -22950,38 +22990,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>231.34</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-DC2F2ECAE7DC</t>
         </is>
@@ -23061,38 +23106,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>314.2</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-22D0A7C5D6C9</t>
         </is>
@@ -23172,38 +23222,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>229.93</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-40B00481C159</t>
         </is>
@@ -23283,38 +23338,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>115.04</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-DBEE440179B9</t>
         </is>
@@ -23394,38 +23454,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>420.02</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-A863B7509137</t>
         </is>
@@ -23505,38 +23570,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>159.15</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-6BEB076C7702</t>
         </is>
@@ -23616,38 +23686,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>440.3</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-0B0EAD078430</t>
         </is>
@@ -23727,38 +23802,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>48.7</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-CB9C595DFD13</t>
         </is>
@@ -23838,38 +23918,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>360.06</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-EA40AF6E46CB</t>
         </is>
@@ -23949,38 +24034,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>34.38</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-4365AD6D77D6</t>
         </is>
@@ -24060,38 +24150,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>391.22</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-0CBCC0572731</t>
         </is>
@@ -24171,38 +24266,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>436.65</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-2B03B82A2CA3</t>
         </is>
@@ -24282,38 +24382,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>222.65</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-3206188A6EAC</t>
         </is>
